--- a/artfynd/A 30155-2021 artfynd.xlsx
+++ b/artfynd/A 30155-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30155-2021 artfynd.xlsx
+++ b/artfynd/A 30155-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,6 +929,120 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122665127</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57400</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Överlöt, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>635027</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6532466</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lästringe</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Helseth</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Helseth</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30155-2021 artfynd.xlsx
+++ b/artfynd/A 30155-2021 artfynd.xlsx
@@ -934,7 +934,7 @@
         <v>122665127</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 30155-2021 artfynd.xlsx
+++ b/artfynd/A 30155-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115647148</v>
+        <v>122665127</v>
       </c>
       <c r="B3" t="n">
-        <v>57181</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,16 +823,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -889,22 +889,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,129 +909,15 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Barbara Leibiger</t>
+          <t>Anders Helseth</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingo Leibiger, Barbara Leibiger</t>
+          <t>Anders Helseth</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>122665127</v>
-      </c>
-      <c r="B4" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Överlöt, Srm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>635027</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6532466</v>
-      </c>
-      <c r="S4" t="n">
-        <v>50</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Nyköping</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Lästringe</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Anders Helseth</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Anders Helseth</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
